--- a/data/trans_orig/P16A08-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A08-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21008</t>
+          <t>20974</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8637</t>
+          <t>8376</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22966</t>
+          <t>23508</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17928</t>
+          <t>17961</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39387</t>
+          <t>38884</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>671986</t>
+          <t>672020</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>686393</t>
+          <t>686795</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>665385</t>
+          <t>664843</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>679714</t>
+          <t>679975</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1341958</t>
+          <t>1342461</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1363417</t>
+          <t>1363384</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14725</t>
+          <t>14662</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36091</t>
+          <t>35447</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24649</t>
+          <t>24500</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49722</t>
+          <t>47970</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44987</t>
+          <t>44966</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75788</t>
+          <t>77664</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>925709</t>
+          <t>926353</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>947075</t>
+          <t>947138</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>918671</t>
+          <t>920423</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>943744</t>
+          <t>943893</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1854405</t>
+          <t>1852529</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1885206</t>
+          <t>1885227</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>8476</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24848</t>
+          <t>25955</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20535</t>
+          <t>20298</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42412</t>
+          <t>41739</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33158</t>
+          <t>32368</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62066</t>
+          <t>59703</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>653661</t>
+          <t>652554</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>670234</t>
+          <t>670033</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>641429</t>
+          <t>642102</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>663306</t>
+          <t>663543</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1300284</t>
+          <t>1302647</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1329192</t>
+          <t>1329982</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18876</t>
+          <t>18845</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41792</t>
+          <t>40213</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37782</t>
+          <t>39282</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66856</t>
+          <t>67369</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64220</t>
+          <t>62936</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101353</t>
+          <t>97885</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>900430</t>
+          <t>902009</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>923346</t>
+          <t>923377</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>971756</t>
+          <t>971243</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1000830</t>
+          <t>999330</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1879481</t>
+          <t>1882949</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1916614</t>
+          <t>1917898</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61545</t>
+          <t>61076</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98468</t>
+          <t>96429</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>110742</t>
+          <t>110391</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>154949</t>
+          <t>157218</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>180513</t>
+          <t>182254</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>242450</t>
+          <t>242954</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3177057</t>
+          <t>3179096</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3213980</t>
+          <t>3214449</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3224248</t>
+          <t>3221979</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3268455</t>
+          <t>3268806</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6412272</t>
+          <t>6411768</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6474209</t>
+          <t>6472468</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8950</t>
+          <t>8292</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24997</t>
+          <t>24928</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21106</t>
+          <t>21199</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43444</t>
+          <t>42219</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33857</t>
+          <t>33771</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60756</t>
+          <t>60552</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>675767</t>
+          <t>675836</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>691814</t>
+          <t>692472</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>649907</t>
+          <t>651132</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>672245</t>
+          <t>672152</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1333359</t>
+          <t>1333563</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1360258</t>
+          <t>1360344</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24547</t>
+          <t>25646</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50989</t>
+          <t>49620</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45849</t>
+          <t>45987</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74832</t>
+          <t>77382</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76216</t>
+          <t>75511</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116226</t>
+          <t>118781</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>966958</t>
+          <t>968327</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>993400</t>
+          <t>992301</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>951856</t>
+          <t>949306</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>980839</t>
+          <t>980701</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1928409</t>
+          <t>1925854</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1968419</t>
+          <t>1969124</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20197</t>
+          <t>19835</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47327</t>
+          <t>44459</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,82 +3381,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>5,88%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>44092</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>31253</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>58176</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5,68%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>7,49%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>74908</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>59157</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>95976</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>6,26%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>44092</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>32079</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>61903</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>4,13%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>74908</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>57395</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>93712</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>709211</t>
+          <t>712079</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>736341</t>
+          <t>736703</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,82 +3494,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>94,12%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,38%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>732191</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>718107</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>745030</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>94,32%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>92,51%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>95,97%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1457913</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1436845</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1473664</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>95,11%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>93,74%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,33%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>732191</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>714380</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>744204</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,32%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>92,03%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>95,87%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1327</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1457913</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1439109</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1475426</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>95,11%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>93,89%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23321</t>
+          <t>23604</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46570</t>
+          <t>48111</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46999</t>
+          <t>46019</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77595</t>
+          <t>76089</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76242</t>
+          <t>75463</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115234</t>
+          <t>114631</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>897369</t>
+          <t>895828</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>920618</t>
+          <t>920335</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>971168</t>
+          <t>972674</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1001764</t>
+          <t>1002744</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1877469</t>
+          <t>1878072</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1916461</t>
+          <t>1917240</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97114</t>
+          <t>94908</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>140864</t>
+          <t>139426</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>169425</t>
+          <t>167870</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>224957</t>
+          <t>224586</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>274781</t>
+          <t>279694</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>349313</t>
+          <t>352409</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3278324</t>
+          <t>3279762</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3322074</t>
+          <t>3324280</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3320129</t>
+          <t>3320500</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3375661</t>
+          <t>3377216</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6614961</t>
+          <t>6611865</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6689493</t>
+          <t>6684580</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11203</t>
+          <t>10960</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28296</t>
+          <t>29540</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15201</t>
+          <t>15395</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36821</t>
+          <t>34913</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30216</t>
+          <t>30221</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57175</t>
+          <t>56316</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>646504</t>
+          <t>645260</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>663597</t>
+          <t>663840</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>636018</t>
+          <t>637926</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>657638</t>
+          <t>657444</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1290464</t>
+          <t>1291323</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1317423</t>
+          <t>1317418</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19039</t>
+          <t>18960</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40327</t>
+          <t>41899</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46440</t>
+          <t>45947</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78508</t>
+          <t>77188</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70360</t>
+          <t>72181</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109848</t>
+          <t>111711</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>982104</t>
+          <t>980532</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1003392</t>
+          <t>1003471</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>964405</t>
+          <t>965725</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>996473</t>
+          <t>996966</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1955496</t>
+          <t>1953633</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1994984</t>
+          <t>1993163</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14659</t>
+          <t>14693</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35395</t>
+          <t>33582</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41226</t>
+          <t>42124</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70162</t>
+          <t>71655</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60396</t>
+          <t>61519</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94017</t>
+          <t>96026</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>724157</t>
+          <t>725970</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>744893</t>
+          <t>744859</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>714849</t>
+          <t>713356</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>743785</t>
+          <t>742887</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1450546</t>
+          <t>1448537</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1484167</t>
+          <t>1483044</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23956</t>
+          <t>23883</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45863</t>
+          <t>47883</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38201</t>
+          <t>38712</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67554</t>
+          <t>67764</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69076</t>
+          <t>66282</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105460</t>
+          <t>104207</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>891704</t>
+          <t>889684</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>913611</t>
+          <t>913684</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>976225</t>
+          <t>976015</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1005578</t>
+          <t>1005067</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1875886</t>
+          <t>1877139</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1912270</t>
+          <t>1915064</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85287</t>
+          <t>85196</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>125454</t>
+          <t>126112</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>163880</t>
+          <t>165895</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>219774</t>
+          <t>218225</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>259786</t>
+          <t>262087</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>330773</t>
+          <t>332000</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3268896</t>
+          <t>3268238</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3309063</t>
+          <t>3309154</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3324768</t>
+          <t>3326317</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3380662</t>
+          <t>3378647</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6608119</t>
+          <t>6606892</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6679106</t>
+          <t>6676805</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11491</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>32674</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20342</t>
+          <t>19820</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41266</t>
+          <t>41194</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37708</t>
+          <t>37128</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65094</t>
+          <t>67227</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>602934</t>
+          <t>602277</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>623460</t>
+          <t>623475</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>634156</t>
+          <t>634228</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>655080</t>
+          <t>655602</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1245279</t>
+          <t>1243146</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1272665</t>
+          <t>1273245</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15983</t>
+          <t>15187</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53307</t>
+          <t>53261</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26191</t>
+          <t>25406</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47886</t>
+          <t>47097</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44566</t>
+          <t>44818</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>87919</t>
+          <t>90186</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1139557</t>
+          <t>1139603</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1176881</t>
+          <t>1177677</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>910220</t>
+          <t>911009</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>931915</t>
+          <t>932700</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2063052</t>
+          <t>2060785</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2106405</t>
+          <t>2106153</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21615</t>
+          <t>21159</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47612</t>
+          <t>47036</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19019</t>
+          <t>18658</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52964</t>
+          <t>53066</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44996</t>
+          <t>43101</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88193</t>
+          <t>91075</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>656072</t>
+          <t>656648</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>682069</t>
+          <t>682525</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>879836</t>
+          <t>879734</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>913781</t>
+          <t>914142</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1548291</t>
+          <t>1545409</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1591488</t>
+          <t>1593383</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17858</t>
+          <t>18116</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41998</t>
+          <t>42926</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56246</t>
+          <t>57749</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>305673</t>
+          <t>325488</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82540</t>
+          <t>82567</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>408562</t>
+          <t>390387</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>884833</t>
+          <t>883905</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>908973</t>
+          <t>908715</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>785701</t>
+          <t>765886</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1035128</t>
+          <t>1033625</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1609643</t>
+          <t>1627818</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1935665</t>
+          <t>1935638</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>84475</t>
+          <t>83532</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>143314</t>
+          <t>141710</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>152869</t>
+          <t>153989</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>463207</t>
+          <t>503983</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>261143</t>
+          <t>263416</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>625379</t>
+          <t>574729</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3315016</t>
+          <t>3316620</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3373855</t>
+          <t>3374798</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3194495</t>
+          <t>3153719</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3504833</t>
+          <t>3503713</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6490653</t>
+          <t>6541303</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6854889</t>
+          <t>6852616</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A08-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A08-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6199</t>
+          <t>6779</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20974</t>
+          <t>19631</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8376</t>
+          <t>8833</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23508</t>
+          <t>23955</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17961</t>
+          <t>18448</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38884</t>
+          <t>37520</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>672020</t>
+          <t>673363</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>686795</t>
+          <t>686215</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>664843</t>
+          <t>664396</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>679975</t>
+          <t>679518</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1342461</t>
+          <t>1343825</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1363384</t>
+          <t>1362897</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14662</t>
+          <t>14326</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35447</t>
+          <t>35458</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24500</t>
+          <t>24459</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47970</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44966</t>
+          <t>44633</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77664</t>
+          <t>76488</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>926353</t>
+          <t>926342</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>947138</t>
+          <t>947474</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>920423</t>
+          <t>918804</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>943893</t>
+          <t>943934</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1852529</t>
+          <t>1853705</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1885227</t>
+          <t>1885560</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8476</t>
+          <t>8651</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25955</t>
+          <t>25388</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20298</t>
+          <t>20560</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41739</t>
+          <t>41691</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32368</t>
+          <t>32438</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59703</t>
+          <t>59073</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>652554</t>
+          <t>653121</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>670033</t>
+          <t>669858</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>642102</t>
+          <t>642150</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>663543</t>
+          <t>663281</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1302647</t>
+          <t>1303277</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1329982</t>
+          <t>1329912</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18845</t>
+          <t>18258</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40213</t>
+          <t>41262</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39282</t>
+          <t>38144</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67369</t>
+          <t>68022</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62936</t>
+          <t>63659</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97885</t>
+          <t>98717</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>902009</t>
+          <t>900960</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>923377</t>
+          <t>923964</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>971243</t>
+          <t>970590</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>999330</t>
+          <t>1000468</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1882949</t>
+          <t>1882117</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1917898</t>
+          <t>1917175</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61076</t>
+          <t>61806</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96429</t>
+          <t>97361</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>110391</t>
+          <t>112128</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>157218</t>
+          <t>156802</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>182254</t>
+          <t>181916</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>242954</t>
+          <t>238183</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3179096</t>
+          <t>3178164</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3214449</t>
+          <t>3213719</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3221979</t>
+          <t>3222395</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3268806</t>
+          <t>3267069</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6411768</t>
+          <t>6416539</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6472468</t>
+          <t>6472806</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8292</t>
+          <t>8777</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24928</t>
+          <t>23523</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21199</t>
+          <t>20989</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42219</t>
+          <t>42634</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33771</t>
+          <t>34415</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60552</t>
+          <t>60284</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>675836</t>
+          <t>677241</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>692472</t>
+          <t>691987</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>651132</t>
+          <t>650717</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>672152</t>
+          <t>672362</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1333563</t>
+          <t>1333831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1360344</t>
+          <t>1359700</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25646</t>
+          <t>25983</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49620</t>
+          <t>49897</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45987</t>
+          <t>45235</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>77382</t>
+          <t>76732</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75511</t>
+          <t>75225</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>118781</t>
+          <t>115920</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>968327</t>
+          <t>968050</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>992301</t>
+          <t>991964</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>949306</t>
+          <t>949956</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>980701</t>
+          <t>981453</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1925854</t>
+          <t>1928715</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1969124</t>
+          <t>1969410</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19835</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44459</t>
+          <t>45277</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31253</t>
+          <t>32159</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58176</t>
+          <t>58191</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59157</t>
+          <t>58418</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95976</t>
+          <t>94572</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>712079</t>
+          <t>711261</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>736703</t>
+          <t>736609</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>718107</t>
+          <t>718092</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>745030</t>
+          <t>744124</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1436845</t>
+          <t>1438249</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1473664</t>
+          <t>1474403</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23604</t>
+          <t>23781</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48111</t>
+          <t>48138</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46019</t>
+          <t>47098</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76089</t>
+          <t>78119</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75463</t>
+          <t>77246</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114631</t>
+          <t>116441</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>895828</t>
+          <t>895801</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>920335</t>
+          <t>920158</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>972674</t>
+          <t>970644</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1002744</t>
+          <t>1001665</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1878072</t>
+          <t>1876262</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1917240</t>
+          <t>1915457</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>94908</t>
+          <t>95064</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>139426</t>
+          <t>139924</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>167870</t>
+          <t>167255</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>224586</t>
+          <t>223801</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>279694</t>
+          <t>278194</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>352409</t>
+          <t>348033</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3279762</t>
+          <t>3279264</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3324280</t>
+          <t>3324124</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3320500</t>
+          <t>3321285</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3377216</t>
+          <t>3377831</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6611865</t>
+          <t>6616241</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6684580</t>
+          <t>6686080</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10960</t>
+          <t>10724</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29540</t>
+          <t>27215</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15395</t>
+          <t>16210</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34913</t>
+          <t>36567</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30221</t>
+          <t>30703</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56316</t>
+          <t>56382</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>645260</t>
+          <t>647585</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>663840</t>
+          <t>664076</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>637926</t>
+          <t>636272</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>657444</t>
+          <t>656629</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1291323</t>
+          <t>1291257</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1317418</t>
+          <t>1316936</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18960</t>
+          <t>19308</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41899</t>
+          <t>42342</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45947</t>
+          <t>47396</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>77188</t>
+          <t>78562</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72181</t>
+          <t>71876</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111711</t>
+          <t>110182</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>980532</t>
+          <t>980089</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1003471</t>
+          <t>1003123</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>965725</t>
+          <t>964351</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>996966</t>
+          <t>995517</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1953633</t>
+          <t>1955162</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1993163</t>
+          <t>1993468</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14693</t>
+          <t>15704</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33582</t>
+          <t>35575</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42124</t>
+          <t>40473</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71655</t>
+          <t>69513</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61519</t>
+          <t>61183</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96026</t>
+          <t>95432</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>725970</t>
+          <t>723977</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>744859</t>
+          <t>743848</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>713356</t>
+          <t>715498</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>742887</t>
+          <t>744538</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1448537</t>
+          <t>1449131</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1483044</t>
+          <t>1483380</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23883</t>
+          <t>23624</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47883</t>
+          <t>48362</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38712</t>
+          <t>38413</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67764</t>
+          <t>68447</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66282</t>
+          <t>69210</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>104207</t>
+          <t>108752</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>889684</t>
+          <t>889205</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>913684</t>
+          <t>913943</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>976015</t>
+          <t>975332</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1005067</t>
+          <t>1005366</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1877139</t>
+          <t>1872594</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1915064</t>
+          <t>1912136</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85196</t>
+          <t>87399</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>126112</t>
+          <t>125072</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>165895</t>
+          <t>163853</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>218225</t>
+          <t>221970</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>262087</t>
+          <t>261314</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>332000</t>
+          <t>327835</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3268238</t>
+          <t>3269278</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3309154</t>
+          <t>3306951</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3326317</t>
+          <t>3322572</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3378647</t>
+          <t>3380689</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6606892</t>
+          <t>6611057</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6676805</t>
+          <t>6677578</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,23%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>20989</t>
+          <t>22143</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>14005</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32674</t>
+          <t>36483</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>29226</t>
+          <t>31326</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19820</t>
+          <t>22431</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41194</t>
+          <t>43234</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>50216</t>
+          <t>53469</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37128</t>
+          <t>39846</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67227</t>
+          <t>71098</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>613962</t>
+          <t>668072</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>602277</t>
+          <t>653732</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>623475</t>
+          <t>676210</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>646196</t>
+          <t>701456</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>634228</t>
+          <t>689548</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>655602</t>
+          <t>710351</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1260157</t>
+          <t>1369528</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1243146</t>
+          <t>1351899</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1273245</t>
+          <t>1383151</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634951</t>
+          <t>690215</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634951</t>
+          <t>690215</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634951</t>
+          <t>690215</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>732782</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>732782</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>732782</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310373</t>
+          <t>1422997</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310373</t>
+          <t>1422997</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310373</t>
+          <t>1422997</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32277</t>
+          <t>32897</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15187</t>
+          <t>22353</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53261</t>
+          <t>49119</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>40438</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25406</t>
+          <t>30460</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47097</t>
+          <t>53980</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>67216</t>
+          <t>73334</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44818</t>
+          <t>56790</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90186</t>
+          <t>92757</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1160587</t>
+          <t>1016020</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1139603</t>
+          <t>999798</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1177677</t>
+          <t>1026564</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>923167</t>
+          <t>1030400</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>911009</t>
+          <t>1016858</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>932700</t>
+          <t>1040378</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2083755</t>
+          <t>2046421</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2060785</t>
+          <t>2026998</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2106153</t>
+          <t>2062965</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>31828</t>
+          <t>34179</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>24079</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47036</t>
+          <t>51016</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38088</t>
+          <t>48927</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18658</t>
+          <t>36963</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53066</t>
+          <t>62364</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>69917</t>
+          <t>83106</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43101</t>
+          <t>66947</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91075</t>
+          <t>100619</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>671856</t>
+          <t>767907</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>656648</t>
+          <t>751070</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>682525</t>
+          <t>778007</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>894712</t>
+          <t>762736</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>879734</t>
+          <t>749299</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>914142</t>
+          <t>774700</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1566567</t>
+          <t>1530642</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1545409</t>
+          <t>1513129</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1593383</t>
+          <t>1546801</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1636484</t>
+          <t>1613748</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1636484</t>
+          <t>1613748</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1636484</t>
+          <t>1613748</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27584</t>
+          <t>30327</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18116</t>
+          <t>19768</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42926</t>
+          <t>43829</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>127428</t>
+          <t>64231</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57749</t>
+          <t>51442</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>325488</t>
+          <t>79802</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>155012</t>
+          <t>94558</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82567</t>
+          <t>77801</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>390387</t>
+          <t>114244</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>899247</t>
+          <t>959735</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>883905</t>
+          <t>946233</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>908715</t>
+          <t>970294</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>963946</t>
+          <t>1052800</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>765886</t>
+          <t>1037229</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1033625</t>
+          <t>1065589</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1863193</t>
+          <t>2012535</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1627818</t>
+          <t>1992849</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1935638</t>
+          <t>2029292</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>112679</t>
+          <t>119545</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83532</t>
+          <t>99673</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>141710</t>
+          <t>146731</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>229682</t>
+          <t>184921</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>153989</t>
+          <t>162551</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>503983</t>
+          <t>211185</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>342361</t>
+          <t>304467</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>263416</t>
+          <t>273514</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>574729</t>
+          <t>339927</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3345651</t>
+          <t>3411735</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3316620</t>
+          <t>3384549</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3374798</t>
+          <t>3431607</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3428020</t>
+          <t>3547392</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3153719</t>
+          <t>3521128</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3503713</t>
+          <t>3569762</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6773671</t>
+          <t>6959126</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6541303</t>
+          <t>6923666</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6852616</t>
+          <t>6990079</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,23%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
